--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Block.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Block.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.252</t>
+    <t xml:space="preserve">EA 23.260</t>
   </si>
   <si>
     <t xml:space="preserve">1</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Block.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Block.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.260</t>
+    <t xml:space="preserve">EA 23.267</t>
   </si>
   <si>
     <t xml:space="preserve">1</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Block.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Block.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.267</t>
+    <t xml:space="preserve">EA 23.281</t>
   </si>
   <si>
     <t xml:space="preserve">1</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Block.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Block.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.281</t>
+    <t xml:space="preserve">EA 23.282 Patch 2</t>
   </si>
   <si>
     <t xml:space="preserve">1</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Block.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Block.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1047" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="572">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -1697,6 +1697,48 @@
   </si>
   <si>
     <t xml:space="preserve">エイリアンのブロック</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">에일리언 벽</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alien wall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">エイリアンの壁</t>
+  </si>
+  <si>
+    <t xml:space="preserve">209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">210</t>
+  </si>
+  <si>
+    <t xml:space="preserve">211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">에일리언 기둥</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alien pillar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">エイリアンの柱</t>
+  </si>
+  <si>
+    <t xml:space="preserve">212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">213</t>
   </si>
 </sst>
 </file>
@@ -1925,7 +1967,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H209"/>
+  <dimension ref="A1:H216"/>
   <sheetFormatPr defaultColWidth="8.7578125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="1" style="0" width="16.15"/>
@@ -5486,6 +5528,125 @@
       </c>
       <c r="E209" s="0" t="s">
         <v>557</v>
+      </c>
+    </row>
+    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A210" s="0" t="s">
+        <v>558</v>
+      </c>
+      <c r="B210" s="0" t="s">
+        <v>559</v>
+      </c>
+      <c r="C210" s="0" t="s">
+        <v>555</v>
+      </c>
+      <c r="D210" s="0" t="s">
+        <v>556</v>
+      </c>
+      <c r="E210" s="0" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A211" s="0" t="s">
+        <v>560</v>
+      </c>
+      <c r="B211" s="0" t="s">
+        <v>559</v>
+      </c>
+      <c r="C211" s="0" t="s">
+        <v>561</v>
+      </c>
+      <c r="D211" s="0" t="s">
+        <v>562</v>
+      </c>
+      <c r="E211" s="0" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A212" s="0" t="s">
+        <v>564</v>
+      </c>
+      <c r="B212" s="0" t="s">
+        <v>559</v>
+      </c>
+      <c r="C212" s="0" t="s">
+        <v>561</v>
+      </c>
+      <c r="D212" s="0" t="s">
+        <v>562</v>
+      </c>
+      <c r="E212" s="0" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A213" s="0" t="s">
+        <v>565</v>
+      </c>
+      <c r="B213" s="0" t="s">
+        <v>559</v>
+      </c>
+      <c r="C213" s="0" t="s">
+        <v>561</v>
+      </c>
+      <c r="D213" s="0" t="s">
+        <v>562</v>
+      </c>
+      <c r="E213" s="0" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A214" s="0" t="s">
+        <v>566</v>
+      </c>
+      <c r="B214" s="0" t="s">
+        <v>559</v>
+      </c>
+      <c r="C214" s="0" t="s">
+        <v>567</v>
+      </c>
+      <c r="D214" s="0" t="s">
+        <v>568</v>
+      </c>
+      <c r="E214" s="0" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A215" s="0" t="s">
+        <v>570</v>
+      </c>
+      <c r="B215" s="0" t="s">
+        <v>559</v>
+      </c>
+      <c r="C215" s="0" t="s">
+        <v>567</v>
+      </c>
+      <c r="D215" s="0" t="s">
+        <v>568</v>
+      </c>
+      <c r="E215" s="0" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A216" s="0" t="s">
+        <v>571</v>
+      </c>
+      <c r="B216" s="0" t="s">
+        <v>559</v>
+      </c>
+      <c r="C216" s="0" t="s">
+        <v>567</v>
+      </c>
+      <c r="D216" s="0" t="s">
+        <v>568</v>
+      </c>
+      <c r="E216" s="0" t="s">
+        <v>569</v>
       </c>
     </row>
   </sheetData>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Block.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Block.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.307</t>
+    <t xml:space="preserve">EA 23.325</t>
   </si>
   <si>
     <t xml:space="preserve">1</t>
